--- a/real_estate_forms/014_residential_tenancy_reference_request_form--real_estate_forms.xlsx
+++ b/real_estate_forms/014_residential_tenancy_reference_request_form--real_estate_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Address</t>
+          <t>Property Address</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>City</t>
+          <t>Property City</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>State</t>
+          <t>Property State</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Post Code</t>
+          <t>Property Postal Code</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Landlord Phone</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Landlord Name</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Landlord Email</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="49" customWidth="1" min="2" max="2"/>
-    <col width="49" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'primary',_'label':_'primary'}</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'primary', 'label': 'Primary'}</t>
+          <t>Primary</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'secondary',_'label':_'secondary'}</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'secondary', 'label': 'Secondary'}</t>
+          <t>Secondary</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'residential',_'label':_'residential'}</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'residential', 'label': 'Residential'}</t>
+          <t>Residential</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'commercial',_'label':_'commercial'}</t>
+          <t>commercial</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'commercial', 'label': 'Commercial'}</t>
+          <t>Commercial</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'rented',_'label':_'rented'}</t>
+          <t>rented</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'rented', 'label': 'Rented'}</t>
+          <t>Rented</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'vacant',_'label':_'vacant'}</t>
+          <t>vacant</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'vacant', 'label': 'Vacant'}</t>
+          <t>Vacant</t>
         </is>
       </c>
     </row>
